--- a/enhancements/test-files/10_Report_pc0606_2026_JanJul.xlsx
+++ b/enhancements/test-files/10_Report_pc0606_2026_JanJul.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,14 +489,49 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>Producer Code</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Producer Name</t>
         </is>
@@ -513,12 +548,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -527,23 +562,48 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20713.21</v>
+        <v>10042.71</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>46026</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>45982</v>
+        <v>45864</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>46026</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1205.13</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>843.59</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>P100</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Pinnacle Agency Partners</t>
         </is>
@@ -560,12 +620,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -574,23 +634,48 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22078</v>
+        <v>15562.16</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>46029</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>45861</v>
+        <v>45747</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46024</v>
-      </c>
-      <c r="L6" t="inlineStr">
+        <v>46025</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1867.46</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>971.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P6" t="n">
+        <v>896.38</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>P101</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Apex Insurance Brokers</t>
         </is>
@@ -612,7 +697,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -621,23 +706,48 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1497.87</v>
+        <v>5810.13</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>46032</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>45823</v>
+        <v>45803</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46028</v>
-      </c>
-      <c r="L7" t="inlineStr">
+        <v>46030</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>697.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P7" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>P102</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Metro Agency Group</t>
         </is>
@@ -650,7 +760,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44289.08</v>
+        <v>31415</v>
       </c>
     </row>
     <row r="10">
@@ -678,23 +788,48 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8808.549999999999</v>
+        <v>18958.64</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>46060</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>45936</v>
+        <v>45994</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46057</v>
-      </c>
-      <c r="L10" t="inlineStr">
+        <v>46060</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2275.04</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1569.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P10" t="n">
+        <v>705.26</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>P103</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Coastal Risk Advisors</t>
         </is>
@@ -711,12 +846,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -725,23 +860,48 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13937.59</v>
+        <v>13777.19</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45992</v>
+        <v>45868</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46058</v>
-      </c>
-      <c r="L11" t="inlineStr">
+        <v>46060</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1653.26</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>925.83</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P11" t="n">
+        <v>727.4299999999999</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>P104</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Brown &amp; Brown</t>
         </is>
@@ -758,12 +918,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -772,16 +932,41 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13636.75</v>
+        <v>5902.58</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>46066</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>45883</v>
+        <v>45914</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46062</v>
+        <v>46065</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>708.3099999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>396.65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P12" t="n">
+        <v>311.66</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +976,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>36382.89</v>
+        <v>38638.41</v>
       </c>
     </row>
     <row r="15">
@@ -805,7 +990,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -819,16 +1004,41 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7507.08</v>
+        <v>19538.31</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>45897</v>
+        <v>46048</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46087</v>
+        <v>46086</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2344.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1477.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="P15" t="n">
+        <v>867.5</v>
       </c>
     </row>
     <row r="16">
@@ -842,12 +1052,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -856,16 +1066,41 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14387.82</v>
+        <v>1882.82</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>46094</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>45964</v>
+        <v>45892</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46092</v>
+        <v>46094</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>225.94</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>94.89</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="P16" t="n">
+        <v>131.05</v>
       </c>
     </row>
     <row r="17">
@@ -879,12 +1114,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -893,16 +1128,41 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2846.51</v>
+        <v>17534.14</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>46097</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>45967</v>
+        <v>45978</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>46095</v>
+        <v>46097</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2104.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1346.62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="P17" t="n">
+        <v>757.48</v>
       </c>
     </row>
     <row r="18">
@@ -912,7 +1172,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>24741.41</v>
+        <v>38955.27</v>
       </c>
     </row>
     <row r="20">
@@ -926,12 +1186,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -940,16 +1200,41 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5216.01</v>
+        <v>4189.27</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>45957</v>
+        <v>45859</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46122</v>
+        <v>46123</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>502.71</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>286.54</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P20" t="n">
+        <v>216.17</v>
       </c>
     </row>
     <row r="21">
@@ -963,12 +1248,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -977,17 +1262,42 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18069.4</v>
+        <v>10195.82</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>46094</v>
+        <v>45874</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>46124</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1223.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>770.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="P21" t="n">
+        <v>452.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1000,12 +1310,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1014,16 +1324,41 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1942.66</v>
+        <v>14319.45</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>46131</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>45904</v>
+        <v>46069</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46130</v>
+        <v>46131</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1718.33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>996.63</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="P22" t="n">
+        <v>721.7</v>
       </c>
     </row>
     <row r="23">
@@ -1033,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>25228.07</v>
+        <v>28704.54</v>
       </c>
     </row>
     <row r="25">
@@ -1047,12 +1382,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1061,16 +1396,41 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6020.93</v>
+        <v>9342.4</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>46158</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>46006</v>
+        <v>46036</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46156</v>
+        <v>46157</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1121.09</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>739.92</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>381.17</v>
       </c>
     </row>
     <row r="26">
@@ -1084,12 +1444,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1098,16 +1458,41 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>24105.17</v>
+        <v>19531.01</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>46161</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>45983</v>
+        <v>45942</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46159</v>
+        <v>46157</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2343.72</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1335.92</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1007.8</v>
       </c>
     </row>
     <row r="27">
@@ -1121,12 +1506,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1135,16 +1520,41 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>19431.42</v>
+        <v>12265.23</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>46164</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>45971</v>
+        <v>45945</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46164</v>
+        <v>46161</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1471.83</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>912.53</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>559.3</v>
       </c>
     </row>
     <row r="28">
@@ -1154,7 +1564,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>49557.52</v>
+        <v>41138.64</v>
       </c>
     </row>
     <row r="30">
@@ -1168,12 +1578,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1182,16 +1592,41 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22852.7</v>
+        <v>23813.8</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>46192</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>45900</v>
+        <v>46008</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46191</v>
+        <v>46192</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2857.66</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1200.22</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1657.44</v>
       </c>
     </row>
     <row r="31">
@@ -1205,12 +1640,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1219,16 +1654,41 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16745.86</v>
+        <v>6690.21</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>46144</v>
+        <v>46047</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>46191</v>
+        <v>46195</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>802.83</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>529.87</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="P31" t="n">
+        <v>272.96</v>
       </c>
     </row>
     <row r="32">
@@ -1242,12 +1702,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1256,16 +1716,41 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6005.21</v>
+        <v>9810.34</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>46198</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46186</v>
+        <v>45916</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46196</v>
+        <v>46194</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1177.24</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N32" t="n">
+        <v>765.21</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P32" t="n">
+        <v>412.03</v>
       </c>
     </row>
     <row r="33">
@@ -1275,7 +1760,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>45603.77</v>
+        <v>40314.35</v>
       </c>
     </row>
     <row r="35">
@@ -1289,12 +1774,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1303,16 +1788,41 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3394.21</v>
+        <v>1121.29</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>46130</v>
+        <v>46110</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>46225</v>
+        <v>46221</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N35" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="P35" t="n">
+        <v>55.17</v>
       </c>
     </row>
     <row r="36">
@@ -1326,12 +1836,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1340,17 +1850,42 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20815.49</v>
+        <v>10477.12</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>45973</v>
+        <v>45997</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>46225</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1257.25</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N36" t="n">
+        <v>817.21</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P36" t="n">
+        <v>440.04</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1363,12 +1898,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1377,16 +1912,41 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6327.05</v>
+        <v>7194.9</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46002</v>
+        <v>46045</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>46201</v>
+        <v>46199</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>863.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N37" t="n">
+        <v>466.23</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P37" t="n">
+        <v>397.16</v>
       </c>
     </row>
     <row r="38">
@@ -1396,7 +1956,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>30536.75</v>
+        <v>18793.31</v>
       </c>
     </row>
   </sheetData>
